--- a/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF CALIDAD/IPS CON MEDICION 2 INDICADORES/2 indicadores.xlsx
+++ b/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF CALIDAD/IPS CON MEDICION 2 INDICADORES/2 indicadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Usuariios\prueba\Automatizaciones\SCRIPT_PDFS\SCRIPS_DOCUMENTADOS\PDF CALIDAD\IPS CON MEDICION 2 INDICADORES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78790402-FDF7-4E5C-B7FE-3D01092C710C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F841F625-DDC9-4C2E-8398-FE148D7EE2E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F76B178-B5D4-4098-B7B9-F39AFCAC640C}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$P$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$P$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>campoa</t>
   </si>
@@ -89,64 +89,16 @@
     <t>campot</t>
   </si>
   <si>
-    <t>13.04.2026</t>
-  </si>
-  <si>
     <t>I TRIMESTRE</t>
   </si>
   <si>
-    <t>0718-2024</t>
-  </si>
-  <si>
-    <t>0941-2024</t>
-  </si>
-  <si>
-    <t>0779-2024</t>
-  </si>
-  <si>
-    <t>0710-2024</t>
-  </si>
-  <si>
-    <t>0296-2024</t>
-  </si>
-  <si>
-    <t>0792-2025</t>
-  </si>
-  <si>
-    <t>0943-2024</t>
-  </si>
-  <si>
-    <t>0759-2025</t>
-  </si>
-  <si>
-    <t>0320-2023</t>
-  </si>
-  <si>
-    <t>MEDICINA Y TECNOLOGIA EN SALUD S.A.S.</t>
-  </si>
-  <si>
-    <t>CAJA DE COMPENSACION FAMILIAR DE CALDAS - CONFA</t>
-  </si>
-  <si>
-    <t>ALVARO GARCIA HERRERA</t>
-  </si>
-  <si>
-    <t>E.S.E. HOSPITAL UNIVERSITARIO SAN RAFAEL DE TUNJA</t>
-  </si>
-  <si>
-    <t>CLINICA DE ORTOPEDIA FUNCION Y EDUCACION S.A.S. – ORTOFED S.A.S</t>
-  </si>
-  <si>
-    <t>CLINICA DE MARLY JORGE CAVELIER GAVIRIA SAS</t>
-  </si>
-  <si>
-    <t>OFTALMOS S.A.</t>
-  </si>
-  <si>
-    <t>E.S.E. HOSPITAL UNIVERSITARIO HERNANDO MONCALEANO PERDOMO</t>
-  </si>
-  <si>
-    <t>AMBULANCIAS ARMENIA S.A.S</t>
+    <t>20.04.2026</t>
+  </si>
+  <si>
+    <t>0051-2023</t>
+  </si>
+  <si>
+    <t>ESE HOSPITAL SAN RAFAEL</t>
   </si>
 </sst>
 </file>
@@ -185,16 +137,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -533,15 +482,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0157F28-2581-40E8-9FC3-C11753EC3402}">
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="8" width="11.42578125" style="1"/>
-    <col min="9" max="9" width="11.42578125" style="4"/>
-    <col min="10" max="10" width="17.42578125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" style="3"/>
+    <col min="10" max="10" width="17.42578125" style="3" customWidth="1"/>
     <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.140625" style="1" customWidth="1"/>
@@ -573,10 +522,10 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -598,480 +547,62 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="90" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="120" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E2" s="1">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="F2" s="1">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="G2" s="1">
-        <v>5</v>
+        <f>AVERAGE(E2:F2)</f>
+        <v>4</v>
       </c>
       <c r="H2" s="1">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="I2" s="3">
-        <v>4</v>
+        <f>H2/2</f>
+        <v>36</v>
       </c>
       <c r="J2" s="3">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="K2" s="2" t="str">
-        <f t="shared" ref="K2:K10" si="0">IF(E2&gt;=4,"cumplimiento del indicador","no cumplimiento con el indicador")</f>
+        <f t="shared" ref="K2" si="0">IF(E2&gt;=4,"cumplimiento del indicador","no cumplimiento con el indicador")</f>
         <v>cumplimiento del indicador</v>
       </c>
       <c r="L2" s="2" t="str">
-        <f t="shared" ref="L2:L10" si="1">IF(F2&gt;=4,"cumplimiento del indicador","no cumplimiento con el indicador")</f>
-        <v>cumplimiento del indicador</v>
+        <f t="shared" ref="L2" si="1">IF(F2&gt;=4,"cumplimiento del indicador","no cumplimiento con el indicador")</f>
+        <v>no cumplimiento con el indicador</v>
       </c>
       <c r="M2" s="2" t="str">
-        <f t="shared" ref="M2:M10" si="2">IF(G2&gt;=4,"Cumplimiento en la evaluación de los indicadores.","No cumplimiento en la evaluación de los indicadores.")</f>
+        <f t="shared" ref="M2" si="2">IF(G2&gt;=4,"Cumplimiento en la evaluación de los indicadores.","No cumplimiento en la evaluación de los indicadores.")</f>
         <v>Cumplimiento en la evaluación de los indicadores.</v>
       </c>
       <c r="N2" s="2" t="str">
-        <f t="shared" ref="N2:N10" si="3">IF(G2&gt;=4,"No se requiere plan de mejora.","Se requiere plan de mejora.")</f>
+        <f t="shared" ref="N2" si="3">IF(G2&gt;=4,"No se requiere plan de mejora.","Se requiere plan de mejora.")</f>
         <v>No se requiere plan de mejora.</v>
       </c>
       <c r="O2" s="2" t="str">
-        <f t="shared" ref="O2:O10" si="4">IF(G2&gt;=4,"Se evidencia cumplimiento en la evaluacion de los indicadores.","Se evidencia incumplimiento en la evaluacion de los indicadores.")</f>
-        <v>Se evidencia cumplimiento en la evaluacion de los indicadores.</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="90" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="1">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F3" s="1">
-        <v>5</v>
-      </c>
-      <c r="G3" s="1">
-        <v>4</v>
-      </c>
-      <c r="H3" s="1">
-        <v>224</v>
-      </c>
-      <c r="I3" s="3">
-        <v>112</v>
-      </c>
-      <c r="J3" s="3">
-        <v>112</v>
-      </c>
-      <c r="K3" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>cumplimiento del indicador</v>
-      </c>
-      <c r="L3" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>cumplimiento del indicador</v>
-      </c>
-      <c r="M3" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Cumplimiento en la evaluación de los indicadores.</v>
-      </c>
-      <c r="N3" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>No se requiere plan de mejora.</v>
-      </c>
-      <c r="O3" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Se evidencia cumplimiento en la evaluacion de los indicadores.</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="90" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="1">
-        <v>4.8</v>
-      </c>
-      <c r="F4" s="1">
-        <v>4.8</v>
-      </c>
-      <c r="G4" s="1">
-        <v>4</v>
-      </c>
-      <c r="H4" s="1">
-        <v>232</v>
-      </c>
-      <c r="I4" s="3">
-        <v>116</v>
-      </c>
-      <c r="J4" s="3">
-        <v>116</v>
-      </c>
-      <c r="K4" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>cumplimiento del indicador</v>
-      </c>
-      <c r="L4" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>cumplimiento del indicador</v>
-      </c>
-      <c r="M4" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Cumplimiento en la evaluación de los indicadores.</v>
-      </c>
-      <c r="N4" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>No se requiere plan de mejora.</v>
-      </c>
-      <c r="O4" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Se evidencia cumplimiento en la evaluacion de los indicadores.</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="90" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="1">
-        <v>5</v>
-      </c>
-      <c r="F5" s="1">
-        <v>5</v>
-      </c>
-      <c r="G5" s="1">
-        <v>5</v>
-      </c>
-      <c r="H5" s="1">
-        <v>261</v>
-      </c>
-      <c r="I5" s="3">
-        <v>130</v>
-      </c>
-      <c r="J5" s="3">
-        <v>130</v>
-      </c>
-      <c r="K5" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>cumplimiento del indicador</v>
-      </c>
-      <c r="L5" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>cumplimiento del indicador</v>
-      </c>
-      <c r="M5" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Cumplimiento en la evaluación de los indicadores.</v>
-      </c>
-      <c r="N5" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>No se requiere plan de mejora.</v>
-      </c>
-      <c r="O5" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Se evidencia cumplimiento en la evaluacion de los indicadores.</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="90" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="1">
-        <v>5</v>
-      </c>
-      <c r="F6" s="1">
-        <v>5</v>
-      </c>
-      <c r="G6" s="1">
-        <v>5</v>
-      </c>
-      <c r="H6" s="1">
-        <v>268</v>
-      </c>
-      <c r="I6" s="3">
-        <v>134</v>
-      </c>
-      <c r="J6" s="3">
-        <v>134</v>
-      </c>
-      <c r="K6" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>cumplimiento del indicador</v>
-      </c>
-      <c r="L6" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>cumplimiento del indicador</v>
-      </c>
-      <c r="M6" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Cumplimiento en la evaluación de los indicadores.</v>
-      </c>
-      <c r="N6" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>No se requiere plan de mejora.</v>
-      </c>
-      <c r="O6" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Se evidencia cumplimiento en la evaluacion de los indicadores.</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="90" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="1">
-        <v>4.2</v>
-      </c>
-      <c r="F7" s="1">
-        <v>5</v>
-      </c>
-      <c r="G7" s="1">
-        <v>4</v>
-      </c>
-      <c r="H7" s="1">
-        <v>463</v>
-      </c>
-      <c r="I7" s="3">
-        <v>231</v>
-      </c>
-      <c r="J7" s="3">
-        <v>231</v>
-      </c>
-      <c r="K7" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>cumplimiento del indicador</v>
-      </c>
-      <c r="L7" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>cumplimiento del indicador</v>
-      </c>
-      <c r="M7" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Cumplimiento en la evaluación de los indicadores.</v>
-      </c>
-      <c r="N7" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>No se requiere plan de mejora.</v>
-      </c>
-      <c r="O7" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Se evidencia cumplimiento en la evaluacion de los indicadores.</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="120" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="1">
-        <v>5</v>
-      </c>
-      <c r="F8" s="1">
-        <v>5</v>
-      </c>
-      <c r="G8" s="1">
-        <v>5</v>
-      </c>
-      <c r="H8" s="1">
-        <v>575</v>
-      </c>
-      <c r="I8" s="3">
-        <v>287</v>
-      </c>
-      <c r="J8" s="3">
-        <v>287</v>
-      </c>
-      <c r="K8" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>cumplimiento del indicador</v>
-      </c>
-      <c r="L8" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>cumplimiento del indicador</v>
-      </c>
-      <c r="M8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Cumplimiento en la evaluación de los indicadores.</v>
-      </c>
-      <c r="N8" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>No se requiere plan de mejora.</v>
-      </c>
-      <c r="O8" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Se evidencia cumplimiento en la evaluacion de los indicadores.</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="120" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="1">
-        <v>5</v>
-      </c>
-      <c r="F9" s="1">
-        <v>5</v>
-      </c>
-      <c r="G9" s="1">
-        <v>5</v>
-      </c>
-      <c r="H9" s="1">
-        <v>617</v>
-      </c>
-      <c r="I9" s="3">
-        <v>308</v>
-      </c>
-      <c r="J9" s="3">
-        <v>308</v>
-      </c>
-      <c r="K9" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>cumplimiento del indicador</v>
-      </c>
-      <c r="L9" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>cumplimiento del indicador</v>
-      </c>
-      <c r="M9" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Cumplimiento en la evaluación de los indicadores.</v>
-      </c>
-      <c r="N9" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>No se requiere plan de mejora.</v>
-      </c>
-      <c r="O9" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Se evidencia cumplimiento en la evaluacion de los indicadores.</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="120" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="1">
-        <v>4.8</v>
-      </c>
-      <c r="F10" s="1">
-        <v>5</v>
-      </c>
-      <c r="G10" s="1">
-        <v>4</v>
-      </c>
-      <c r="H10" s="1">
-        <v>712</v>
-      </c>
-      <c r="I10" s="3">
-        <v>356</v>
-      </c>
-      <c r="J10" s="3">
-        <v>356</v>
-      </c>
-      <c r="K10" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>cumplimiento del indicador</v>
-      </c>
-      <c r="L10" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>cumplimiento del indicador</v>
-      </c>
-      <c r="M10" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Cumplimiento en la evaluación de los indicadores.</v>
-      </c>
-      <c r="N10" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>No se requiere plan de mejora.</v>
-      </c>
-      <c r="O10" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="O2" si="4">IF(G2&gt;=4,"Se evidencia cumplimiento en la evaluacion de los indicadores.","Se evidencia incumplimiento en la evaluacion de los indicadores.")</f>
         <v>Se evidencia cumplimiento en la evaluacion de los indicadores.</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P10" xr:uid="{C0157F28-2581-40E8-9FC3-C11753EC3402}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P10">
-      <sortCondition ref="J1:J10"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:P1" xr:uid="{C0157F28-2581-40E8-9FC3-C11753EC3402}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF CALIDAD/IPS CON MEDICION 2 INDICADORES/2 indicadores.xlsx
+++ b/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/PDF CALIDAD/IPS CON MEDICION 2 INDICADORES/2 indicadores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Usuariios\prueba\Automatizaciones\SCRIPT_PDFS\SCRIPS_DOCUMENTADOS\PDF CALIDAD\IPS CON MEDICION 2 INDICADORES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AGS\DESARROLLO\GITHUB\Automatizaciones\SCRIPT_PDFS\SCRIPS_DOCUMENTADOS\PDF CALIDAD\IPS CON MEDICION 2 INDICADORES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F841F625-DDC9-4C2E-8398-FE148D7EE2E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12716E01-D27B-4A53-9B1D-60E3AAB3D9D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7F76B178-B5D4-4098-B7B9-F39AFCAC640C}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{7F76B178-B5D4-4098-B7B9-F39AFCAC640C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -30,16 +30,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
   <si>
     <t>campoa</t>
   </si>
@@ -95,10 +96,58 @@
     <t>20.04.2026</t>
   </si>
   <si>
-    <t>0051-2023</t>
-  </si>
-  <si>
-    <t>ESE HOSPITAL SAN RAFAEL</t>
+    <t>0739-2024</t>
+  </si>
+  <si>
+    <t>0007-2021</t>
+  </si>
+  <si>
+    <t>0954-2024</t>
+  </si>
+  <si>
+    <t>0269-2024</t>
+  </si>
+  <si>
+    <t>0869-2021</t>
+  </si>
+  <si>
+    <t>0669-2024</t>
+  </si>
+  <si>
+    <t>0513-2025</t>
+  </si>
+  <si>
+    <t>0657-2025</t>
+  </si>
+  <si>
+    <t>0631-2025</t>
+  </si>
+  <si>
+    <t>ORTHO WAVE COLOMBIA LTDA</t>
+  </si>
+  <si>
+    <t>HOSPITAL DEPARTAMENTAL FELIPE SUAREZ DE SALAMINA CALDAS E.S.E.</t>
+  </si>
+  <si>
+    <t>HOSPITAL GENERAL SAN ISIDRO EMPRESA SOCIAL DEL ESTADO</t>
+  </si>
+  <si>
+    <t>ESE HOSPITAL MENTAL DE FILANDIA</t>
+  </si>
+  <si>
+    <t>EMPRESA SOCIAL DEL ESTADO HOSPITAL SAN VICENTE DE PAUL.</t>
+  </si>
+  <si>
+    <t>JOSE MARIA NIÑO CAICEDO-ORTOPEDISTA DE RODILLA</t>
+  </si>
+  <si>
+    <t>HOSPITAL SAN LORENZO DE SUPÍA CALDAS</t>
+  </si>
+  <si>
+    <t>CENTRO MEDICO LOS ALJARES IPS SAS</t>
+  </si>
+  <si>
+    <t>UNIDAD ESPECIALIZADA DE REHABILITACIÓN INTEGRAL COOPERATIVA DE TRABAJO ASOCIADO - UERI-CTA</t>
   </si>
 </sst>
 </file>
@@ -108,7 +157,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,16 +165,33 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -133,11 +199,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -148,6 +240,16 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -482,22 +584,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0157F28-2581-40E8-9FC3-C11753EC3402}">
-  <dimension ref="A1:P2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="11.42578125" style="1"/>
-    <col min="9" max="9" width="11.42578125" style="3"/>
-    <col min="10" max="10" width="17.42578125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.140625" style="1" customWidth="1"/>
-    <col min="14" max="15" width="11.42578125" style="1"/>
+    <col min="1" max="1" width="19.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="11.375" style="1"/>
+    <col min="9" max="9" width="11.375" style="3"/>
+    <col min="10" max="10" width="17.375" style="3" customWidth="1"/>
+    <col min="11" max="11" width="13.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.125" style="1" customWidth="1"/>
+    <col min="14" max="15" width="11.375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -547,57 +649,482 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="120" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="85.5">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="7">
+        <v>4</v>
+      </c>
+      <c r="F2" s="7">
+        <v>4</v>
+      </c>
+      <c r="G2" s="1">
+        <f t="shared" ref="G2:G10" si="0">AVERAGE(E2:F2)</f>
+        <v>4</v>
+      </c>
+      <c r="H2" s="6">
+        <v>35</v>
+      </c>
+      <c r="I2" s="3">
+        <v>18</v>
+      </c>
+      <c r="J2" s="3">
+        <v>18</v>
+      </c>
+      <c r="K2" s="2" t="str">
+        <f t="shared" ref="K2:K10" si="1">IF(E2&gt;=4,"cumplimiento del indicador","no cumplimiento con el indicador")</f>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="L2" s="2" t="str">
+        <f t="shared" ref="L2:L10" si="2">IF(F2&gt;=4,"cumplimiento del indicador","no cumplimiento con el indicador")</f>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="M2" s="2" t="str">
+        <f t="shared" ref="M2:M10" si="3">IF(G2&gt;=4,"Cumplimiento en la evaluación de los indicadores.","No cumplimiento en la evaluación de los indicadores.")</f>
+        <v>Cumplimiento en la evaluación de los indicadores.</v>
+      </c>
+      <c r="N2" s="2" t="str">
+        <f t="shared" ref="N2:N10" si="4">IF(G2&gt;=4,"No se requiere plan de mejora.","Se requiere plan de mejora.")</f>
+        <v>No se requiere plan de mejora.</v>
+      </c>
+      <c r="O2" s="2" t="str">
+        <f t="shared" ref="O2:O10" si="5">IF(G2&gt;=4,"Se evidencia cumplimiento en la evaluacion de los indicadores.","Se evidencia incumplimiento en la evaluacion de los indicadores.")</f>
+        <v>Se evidencia cumplimiento en la evaluacion de los indicadores.</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="99.75">
+      <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="1">
+      <c r="E3" s="7">
+        <v>5</v>
+      </c>
+      <c r="F3" s="7">
+        <v>5</v>
+      </c>
+      <c r="G3" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="H3" s="6">
+        <v>14</v>
+      </c>
+      <c r="I3" s="3">
+        <f t="shared" ref="I3:I8" si="6">H3/2</f>
+        <v>7</v>
+      </c>
+      <c r="J3" s="3">
+        <v>7</v>
+      </c>
+      <c r="K3" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="L3" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="M3" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>Cumplimiento en la evaluación de los indicadores.</v>
+      </c>
+      <c r="N3" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>No se requiere plan de mejora.</v>
+      </c>
+      <c r="O3" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>Se evidencia cumplimiento en la evaluacion de los indicadores.</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="85.5">
+      <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="7">
+        <v>5</v>
+      </c>
+      <c r="F4" s="7">
+        <v>5</v>
+      </c>
+      <c r="G4" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="H4" s="6">
+        <v>15</v>
+      </c>
+      <c r="I4" s="3">
+        <v>7</v>
+      </c>
+      <c r="J4" s="3">
+        <v>7</v>
+      </c>
+      <c r="K4" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="L4" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="M4" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>Cumplimiento en la evaluación de los indicadores.</v>
+      </c>
+      <c r="N4" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>No se requiere plan de mejora.</v>
+      </c>
+      <c r="O4" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>Se evidencia cumplimiento en la evaluacion de los indicadores.</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="85.5">
+      <c r="A5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="7">
+        <v>5</v>
+      </c>
+      <c r="F5" s="7">
+        <v>5</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="H5" s="6">
+        <v>17</v>
+      </c>
+      <c r="I5" s="3">
+        <v>8</v>
+      </c>
+      <c r="J5" s="3">
+        <v>8</v>
+      </c>
+      <c r="K5" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="L5" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="M5" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>Cumplimiento en la evaluación de los indicadores.</v>
+      </c>
+      <c r="N5" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>No se requiere plan de mejora.</v>
+      </c>
+      <c r="O5" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>Se evidencia cumplimiento en la evaluacion de los indicadores.</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="99.75">
+      <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="7">
+        <v>5</v>
+      </c>
+      <c r="F6" s="7">
+        <v>3</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="H6" s="6">
+        <v>21</v>
+      </c>
+      <c r="I6" s="3">
+        <v>11</v>
+      </c>
+      <c r="J6" s="3">
+        <v>11</v>
+      </c>
+      <c r="K6" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="L6" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>no cumplimiento con el indicador</v>
+      </c>
+      <c r="M6" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>Cumplimiento en la evaluación de los indicadores.</v>
+      </c>
+      <c r="N6" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>No se requiere plan de mejora.</v>
+      </c>
+      <c r="O6" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>Se evidencia cumplimiento en la evaluacion de los indicadores.</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="85.5">
+      <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="7">
+        <v>5</v>
+      </c>
+      <c r="F7" s="7">
+        <v>5</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="H7" s="6">
+        <v>25</v>
+      </c>
+      <c r="I7" s="3">
+        <v>13</v>
+      </c>
+      <c r="J7" s="3">
+        <v>13</v>
+      </c>
+      <c r="K7" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="L7" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="M7" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>Cumplimiento en la evaluación de los indicadores.</v>
+      </c>
+      <c r="N7" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>No se requiere plan de mejora.</v>
+      </c>
+      <c r="O7" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>Se evidencia cumplimiento en la evaluacion de los indicadores.</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="85.5">
+      <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="7">
+        <v>5</v>
+      </c>
+      <c r="F8" s="7">
+        <v>4</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="0"/>
         <v>4.5</v>
       </c>
-      <c r="F2" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="G2" s="1">
-        <f>AVERAGE(E2:F2)</f>
-        <v>4</v>
-      </c>
-      <c r="H2" s="1">
-        <v>72</v>
-      </c>
-      <c r="I2" s="3">
-        <f>H2/2</f>
-        <v>36</v>
-      </c>
-      <c r="J2" s="3">
-        <v>36</v>
-      </c>
-      <c r="K2" s="2" t="str">
-        <f t="shared" ref="K2" si="0">IF(E2&gt;=4,"cumplimiento del indicador","no cumplimiento con el indicador")</f>
-        <v>cumplimiento del indicador</v>
-      </c>
-      <c r="L2" s="2" t="str">
-        <f t="shared" ref="L2" si="1">IF(F2&gt;=4,"cumplimiento del indicador","no cumplimiento con el indicador")</f>
-        <v>no cumplimiento con el indicador</v>
-      </c>
-      <c r="M2" s="2" t="str">
-        <f t="shared" ref="M2" si="2">IF(G2&gt;=4,"Cumplimiento en la evaluación de los indicadores.","No cumplimiento en la evaluación de los indicadores.")</f>
+      <c r="H8" s="6">
+        <v>30</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="J8" s="3">
+        <v>15</v>
+      </c>
+      <c r="K8" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="L8" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="M8" s="2" t="str">
+        <f t="shared" si="3"/>
         <v>Cumplimiento en la evaluación de los indicadores.</v>
       </c>
-      <c r="N2" s="2" t="str">
-        <f t="shared" ref="N2" si="3">IF(G2&gt;=4,"No se requiere plan de mejora.","Se requiere plan de mejora.")</f>
+      <c r="N8" s="2" t="str">
+        <f t="shared" si="4"/>
         <v>No se requiere plan de mejora.</v>
       </c>
-      <c r="O2" s="2" t="str">
-        <f t="shared" ref="O2" si="4">IF(G2&gt;=4,"Se evidencia cumplimiento en la evaluacion de los indicadores.","Se evidencia incumplimiento en la evaluacion de los indicadores.")</f>
+      <c r="O8" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>Se evidencia cumplimiento en la evaluacion de los indicadores.</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="85.5">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="7">
+        <v>5</v>
+      </c>
+      <c r="F9" s="7">
+        <v>5</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="H9" s="6">
+        <v>33</v>
+      </c>
+      <c r="I9" s="3">
+        <v>17</v>
+      </c>
+      <c r="J9" s="3">
+        <v>17</v>
+      </c>
+      <c r="K9" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="L9" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="M9" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>Cumplimiento en la evaluación de los indicadores.</v>
+      </c>
+      <c r="N9" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>No se requiere plan de mejora.</v>
+      </c>
+      <c r="O9" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>Se evidencia cumplimiento en la evaluacion de los indicadores.</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="156.75">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="7">
+        <v>5</v>
+      </c>
+      <c r="F10" s="7">
+        <v>5</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="H10" s="6">
+        <v>379</v>
+      </c>
+      <c r="I10" s="3">
+        <v>190</v>
+      </c>
+      <c r="J10" s="3">
+        <v>190</v>
+      </c>
+      <c r="K10" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="L10" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>cumplimiento del indicador</v>
+      </c>
+      <c r="M10" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>Cumplimiento en la evaluación de los indicadores.</v>
+      </c>
+      <c r="N10" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v>No se requiere plan de mejora.</v>
+      </c>
+      <c r="O10" s="2" t="str">
+        <f t="shared" si="5"/>
         <v>Se evidencia cumplimiento en la evaluacion de los indicadores.</v>
       </c>
     </row>
